--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-01/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_HYDROGARDENS Ι.Κ.Ε_2026-01.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-01/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_HYDROGARDENS Ι.Κ.Ε_2026-01.xlsx
@@ -699,7 +699,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -974,7 +974,13 @@
     <xf numFmtId="168" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="11" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="12" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2832,7 +2838,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>13/02/26</t>
+          <t>06/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2921,16 +2927,16 @@
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>23514.66</v>
+        <v>22534.89</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>1860.4053999</v>
+        <v>1753.3365132</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>5.88</v>
+        <v>5.63</v>
       </c>
       <c r="G10" s="92" t="n">
-        <v>79.12</v>
+        <v>77.81</v>
       </c>
       <c r="H10" s="93" t="n"/>
     </row>
@@ -3521,36 +3527,36 @@
         </is>
       </c>
       <c r="D40" s="25" t="n">
-        <v>982.8299999999999</v>
+        <v>23337.06</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>106.8339501</v>
+        <v>2474.9167497</v>
       </c>
       <c r="F40" s="25" t="n">
-        <v>0.25</v>
+        <v>5.83</v>
       </c>
       <c r="G40" s="92" t="n">
-        <v>108.7</v>
+        <v>106.05</v>
       </c>
       <c r="H40" s="93" t="n"/>
     </row>
     <row r="41" ht="28.5" customHeight="1" s="76" thickBot="1">
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" s="94" t="inlineStr">
         <is>
           <t>Σύνολο</t>
         </is>
       </c>
-      <c r="D41" s="30" t="n">
-        <v>661545.12</v>
-      </c>
-      <c r="E41" s="30" t="n">
-        <v>72544.99000000001</v>
-      </c>
-      <c r="F41" s="30" t="n">
-        <v>165.39</v>
-      </c>
-      <c r="G41" s="94" t="n">
-        <v>109.66</v>
+      <c r="D41" s="95" t="n">
+        <v>682919.58</v>
+      </c>
+      <c r="E41" s="95" t="n">
+        <v>74806.00999999999</v>
+      </c>
+      <c r="F41" s="95" t="n">
+        <v>170.72</v>
+      </c>
+      <c r="G41" s="96" t="n">
+        <v>109.54</v>
       </c>
       <c r="H41" s="93" t="n"/>
     </row>
@@ -3559,7 +3565,7 @@
       <c r="D42" s="33" t="n"/>
       <c r="E42" s="33" t="n"/>
       <c r="F42" s="34" t="n"/>
-      <c r="G42" s="95" t="n"/>
+      <c r="G42" s="97" t="n"/>
       <c r="H42" s="93" t="n"/>
     </row>
     <row r="43" ht="49" customHeight="1" s="76" thickBot="1">
@@ -3573,16 +3579,16 @@
           <t>Ανάλυση Χρεώσεων και Υπηρεσίων ΦοΣΕ</t>
         </is>
       </c>
-      <c r="C44" s="96" t="n"/>
-      <c r="D44" s="97" t="n"/>
+      <c r="C44" s="98" t="n"/>
+      <c r="D44" s="99" t="n"/>
       <c r="E44" s="18" t="n"/>
-      <c r="F44" s="98" t="inlineStr">
+      <c r="F44" s="100" t="inlineStr">
         <is>
           <t>Υπολογισμός προς καταβολή</t>
         </is>
       </c>
-      <c r="G44" s="96" t="n"/>
-      <c r="H44" s="99" t="n"/>
+      <c r="G44" s="98" t="n"/>
+      <c r="H44" s="101" t="n"/>
       <c r="I44" s="45" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1" s="76">
@@ -3592,7 +3598,7 @@
         </is>
       </c>
       <c r="C45" s="83" t="n"/>
-      <c r="D45" s="100" t="n">
+      <c r="D45" s="102" t="n">
         <v>0.25</v>
       </c>
       <c r="E45" s="44" t="n"/>
@@ -3602,8 +3608,8 @@
         </is>
       </c>
       <c r="G45" s="83" t="n"/>
-      <c r="H45" s="101" t="n">
-        <v>661.55</v>
+      <c r="H45" s="103" t="n">
+        <v>682.92</v>
       </c>
       <c r="I45" s="45" t="n"/>
     </row>
@@ -3613,9 +3619,9 @@
           <t>Σύνολο (€)</t>
         </is>
       </c>
-      <c r="C46" s="102" t="n"/>
-      <c r="D46" s="103" t="n">
-        <v>165.39</v>
+      <c r="C46" s="104" t="n"/>
+      <c r="D46" s="105" t="n">
+        <v>170.72</v>
       </c>
       <c r="E46" s="41" t="n"/>
       <c r="F46" s="60" t="inlineStr">
@@ -3624,8 +3630,8 @@
         </is>
       </c>
       <c r="G46" s="83" t="n"/>
-      <c r="H46" s="101" t="n">
-        <v>72544.99000000001</v>
+      <c r="H46" s="103" t="n">
+        <v>74806.00999999999</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3664,7 +3670,7 @@
           <t xml:space="preserve">Συνολικό Ποσό προς καταβολή </t>
         </is>
       </c>
-      <c r="G49" s="102" t="n"/>
+      <c r="G49" s="104" t="n"/>
       <c r="H49" s="48">
         <f>H46+H47+H48</f>
         <v/>
@@ -3685,16 +3691,16 @@
           <t>Στοιχεία Τράπεζας</t>
         </is>
       </c>
-      <c r="C51" s="96" t="n"/>
-      <c r="D51" s="97" t="n"/>
+      <c r="C51" s="98" t="n"/>
+      <c r="D51" s="99" t="n"/>
       <c r="E51" s="41" t="n"/>
-      <c r="F51" s="98" t="inlineStr">
+      <c r="F51" s="100" t="inlineStr">
         <is>
           <t>Υπολογισμός Τιμολόγησης</t>
         </is>
       </c>
-      <c r="G51" s="96" t="n"/>
-      <c r="H51" s="99" t="n"/>
+      <c r="G51" s="98" t="n"/>
+      <c r="H51" s="101" t="n"/>
       <c r="I51" s="45" t="n"/>
     </row>
     <row r="52" ht="25.25" customHeight="1" s="76">
@@ -3703,12 +3709,12 @@
           <t xml:space="preserve"> ΙΒΑΝ</t>
         </is>
       </c>
-      <c r="C52" s="104" t="inlineStr">
+      <c r="C52" s="106" t="inlineStr">
         <is>
           <t>GR8601105060000050600510049</t>
         </is>
       </c>
-      <c r="D52" s="105" t="n"/>
+      <c r="D52" s="107" t="n"/>
       <c r="E52" s="41" t="n"/>
       <c r="F52" s="60" t="inlineStr">
         <is>
@@ -3728,12 +3734,12 @@
           <t xml:space="preserve"> Ημερομηνία</t>
         </is>
       </c>
-      <c r="C53" s="106" t="inlineStr">
-        <is>
-          <t>15/02/26</t>
-        </is>
-      </c>
-      <c r="D53" s="107" t="n"/>
+      <c r="C53" s="108" t="inlineStr">
+        <is>
+          <t>08/03/26</t>
+        </is>
+      </c>
+      <c r="D53" s="109" t="n"/>
       <c r="E53" s="41" t="n"/>
       <c r="F53" s="60" t="inlineStr">
         <is>
@@ -3757,7 +3763,7 @@
           <t xml:space="preserve">ΓΕΝΙΚΟ ΣΥΝΟΛΟ </t>
         </is>
       </c>
-      <c r="G54" s="102" t="n"/>
+      <c r="G54" s="104" t="n"/>
       <c r="H54" s="43">
         <f>H52+H53</f>
         <v/>
@@ -3766,7 +3772,7 @@
     </row>
     <row r="55" ht="28.75" customHeight="1" s="76"/>
     <row r="56" ht="38.25" customHeight="1" s="76">
-      <c r="B56" s="108" t="inlineStr">
+      <c r="B56" s="110" t="inlineStr">
         <is>
           <t>Σημείωση: Το τελικό ποσό πίστωσης παραγωγού προκύπτει από το άθροισμα των γινομένων της παραγόμενης ενέργειας επί της αντίστοιχης Τιμής Εκκαθάρισης Αγοράς Επόμενης Ημέρας ανά 15', αφαιρώντας την πληρωμή υπηρεσιών ΦοΣΕ και Διαχειριστικών εξόδων. Οι πληρωμές της GREEN VALUE Α.Ε. πραγματοποιουνται εντός 2 εργάσιμων ημερών μετά την παραλαβή του ενημερωτικού σημειώματος.</t>
         </is>
